--- a/nyc_taxi_analysis/03_combinations/ALL_COMBINATIONS_TESTED.xlsx
+++ b/nyc_taxi_analysis/03_combinations/ALL_COMBINATIONS_TESTED.xlsx
@@ -431,27 +431,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X31"/>
+  <dimension ref="A1:X44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="38" customWidth="1" min="4" max="4"/>
     <col width="27" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="20" customWidth="1" min="15" max="15"/>
     <col width="23" customWidth="1" min="16" max="16"/>
-    <col width="23" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="13" customWidth="1" min="21" max="21"/>
@@ -656,17 +656,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>br_e3d9ee52</t>
+          <t>br_4e2a95f5</t>
         </is>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
-          <t>log_trip_duration_minutes; log1p_trip_duration_minutes</t>
+          <t>trip_duration_minutes; log_trip_duration_minutes; log1p_trip_duration_minutes</t>
         </is>
       </c>
       <c r="W2" s="3" t="inlineStr">
         <is>
-          <t>2 equivalent transformation(s) of the same columns gave the same effect within 0.01; reporting the simplest form</t>
+          <t>3 equivalent transformation(s) of the same columns gave the same effect within 0.01; reporting the simplest form</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>br_01bd146e</t>
+          <t>br_4e2a95f5</t>
         </is>
       </c>
       <c r="V3" s="3" t="inlineStr"/>
@@ -756,7 +756,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>passenger_count_times_trip_duration_minutes</t>
+          <t>trip_distance</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>160a090832eb12ff</t>
+          <t>b74d39221ecb6e75</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -780,19 +780,19 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2515206</v>
+        <v>3509466</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6343146751956786</v>
+        <v>0.867421375892653</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8389135286620988</v>
+        <v>0.8473806505494269</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2180679896208855</v>
+        <v>0.2292361220782569</v>
       </c>
       <c r="L4" t="n">
-        <v>0.83891</v>
+        <v>0.86742</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -805,26 +805,26 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>0.9964803378062043</v>
+        <v>0.9982039731820481</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4023551071685993</v>
+        <v>0.7524198433555032</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.613564544126544</v>
+        <v>4.231065593293843</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.84534</v>
+        <v>0.8464699999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>br_01bd146e</t>
+          <t>br_4e2a95f5</t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr"/>
@@ -836,7 +836,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>passenger_count_times_trip_distance</t>
+          <t>fare_per_mile_times_trip_distance</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>f16adabba4cea285</t>
+          <t>f1c1efba631a3dce</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -860,19 +860,19 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2515206</v>
+        <v>3509466</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7806523699016266</v>
+        <v>0.9656760855932028</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8348451180254627</v>
+        <v>0.957081097824685</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2175543936821757</v>
+        <v>0.4216936873096108</v>
       </c>
       <c r="L5" t="n">
-        <v>0.83485</v>
+        <v>0.96568</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -885,26 +885,26 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>0.9974243750597225</v>
+        <v>0.9994051036302739</v>
       </c>
       <c r="P5" t="n">
-        <v>0.609418122633026</v>
+        <v>0.9325303022866108</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.340188523922481</v>
+        <v>1.163133031834264</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.84382</v>
+        <v>0.84488</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>br_01bd146e</t>
+          <t>br_4e2a95f5</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>trip_duration_minutes_per_passenger_count</t>
+          <t>passenger_count_times_trip_distance</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>030c5872b019c3b7</t>
+          <t>f16adabba4cea285</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -940,19 +940,19 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2501017</v>
+        <v>2515206</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6120722130875675</v>
+        <v>0.7806523699016266</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8325199825608567</v>
+        <v>0.8348451180254627</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2094475548676109</v>
+        <v>0.2175543936821757</v>
       </c>
       <c r="L6" t="n">
-        <v>0.83252</v>
+        <v>0.83485</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -965,26 +965,26 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>0.9960813267356198</v>
+        <v>0.9974243750597225</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3746323940339127</v>
+        <v>0.609418122633026</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.9203087006908761</v>
+        <v>2.340188523922481</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.84253</v>
+        <v>0.84382</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>br_01bd146e</t>
+          <t>br_4e2a95f5</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr"/>
@@ -996,7 +996,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>passenger_count_per_trip_duration_minutes</t>
+          <t>passenger_count_per_trip_distance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>bae3420ef854759c</t>
+          <t>db5734034bdaf53a</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1023,16 +1023,16 @@
         <v>2515206</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3204213238207766</v>
+        <v>-0.1591283294608796</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8214823777036389</v>
+        <v>-0.8212728592035911</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2055526169758378</v>
+        <v>0.2139136151440717</v>
       </c>
       <c r="L7" t="n">
-        <v>0.82148</v>
+        <v>0.8212699999999999</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1045,26 +1045,26 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>0.9873057092676598</v>
+        <v>0.9391456907199275</v>
       </c>
       <c r="P7" t="n">
-        <v>0.102669824759059</v>
+        <v>0.02532182523701025</v>
       </c>
       <c r="Q7" t="n">
-        <v>-45.27793351966903</v>
+        <v>-1.271534277845698</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.83585</v>
+        <v>0.82482</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>br_01bd146e</t>
+          <t>br_4e2a95f5</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr"/>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>passenger_count_per_trip_distance</t>
+          <t>average_speed_mph_per_trip_distance</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>db5734034bdaf53a</t>
+          <t>cdf62daa38611534</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1104,19 +1104,19 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2515206</v>
+        <v>3509466</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1591283294608796</v>
+        <v>-0.4255408505515663</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8212728592035911</v>
+        <v>-0.8885380023353529</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2139136151440717</v>
+        <v>0.2505169050856304</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8212699999999999</v>
+        <v>0.88854</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1129,32 +1129,36 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>0.9391456907199275</v>
+        <v>0.9968252404271609</v>
       </c>
       <c r="P8" t="n">
-        <v>0.02532182523701025</v>
+        <v>0.1810850154881505</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.271534277845698</v>
+        <v>-1.593028695922017</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.82482</v>
+        <v>0.81518</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>br_01bd146e</t>
-        </is>
-      </c>
-      <c r="V8" s="3" t="inlineStr"/>
+          <t>br_4e2a95f5</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>trip_distance_per_average_speed_mph</t>
+        </is>
+      </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t>monotonic association is much stronger than the linear one; the relationship is probably nonlinear</t>
+          <t>monotonic association is much stronger than the linear one; the relationship is probably nonlinear; 1 equivalent transformation(s) of the same columns gave the same effect within 0.01; reporting the simplest form</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1168,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>trip_distance_times_trip_duration_minutes</t>
+          <t>log1p_trip_distance</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1174,7 +1178,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>f57010fa3f6db457</t>
+          <t>f141556f75d279df</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1191,16 +1195,16 @@
         <v>3509466</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7412647837185244</v>
+        <v>0.8041207183735763</v>
       </c>
       <c r="I9" t="n">
-        <v>0.895436231049961</v>
+        <v>0.8473806505494269</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2878692159217569</v>
+        <v>0.2292361220782569</v>
       </c>
       <c r="L9" t="n">
-        <v>0.89544</v>
+        <v>0.84738</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1213,26 +1217,26 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>0.9890844447896711</v>
+        <v>0.9989294984333846</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5494734795812708</v>
+        <v>0.6466101297176365</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0613970876549715</v>
+        <v>24.89486382237022</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.81616</v>
+        <v>0.7994599999999999</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>br_01bd146e</t>
+          <t>br_4e2a95f5</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr"/>
@@ -1244,7 +1248,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>log_trip_duration_minutes</t>
+          <t>log_trip_distance</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1254,7 +1258,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ef027e69ae3576f1</t>
+          <t>6de2708a5513d3c8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1271,16 +1275,16 @@
         <v>3509466</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6849326881994786</v>
+        <v>0.7001671976609333</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8885383452608312</v>
+        <v>0.8473806505494269</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2504791798501583</v>
+        <v>0.2292361220782569</v>
       </c>
       <c r="L10" t="n">
-        <v>0.88854</v>
+        <v>0.84738</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1293,31 +1297,31 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>0.9992393614921484</v>
+        <v>0.9982482859237006</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4691327873641642</v>
+        <v>0.4902341046803644</v>
       </c>
       <c r="Q10" t="n">
-        <v>19.82605129442883</v>
+        <v>14.07130464097933</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8157</v>
+        <v>0.79931</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>br_01bd146e</t>
+          <t>br_4e2a95f5</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t>log1p_trip_duration_minutes</t>
+          <t>log1p_trip_distance</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
@@ -1332,7 +1336,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>log1p_trip_distance</t>
+          <t>trip_duration_minutes_per_tip_fraction_of_fare</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1342,7 +1346,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>f141556f75d279df</t>
+          <t>edbd559ad64d5c58</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1356,19 +1360,19 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>3509466</v>
+        <v>2065405</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8041207183735763</v>
+        <v>0.04690825126404342</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8473806505494269</v>
+        <v>0.8097285115033341</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2292361220782569</v>
+        <v>0.1957703996238391</v>
       </c>
       <c r="L11" t="n">
-        <v>0.84738</v>
+        <v>0.8097299999999999</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1381,30 +1385,34 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>0.9989294984333846</v>
+        <v>0.8707572031218791</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6466101297176365</v>
+        <v>0.002200384036650631</v>
       </c>
       <c r="Q11" t="n">
-        <v>24.89486382237022</v>
+        <v>0.0001529366434668021</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7994599999999999</v>
+        <v>0.75626</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>br_01bd146e</t>
+          <t>br_4e2a95f5</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr"/>
-      <c r="W11" s="3" t="inlineStr"/>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>monotonic association is much stronger than the linear one; the relationship is probably nonlinear</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1412,7 +1420,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>trip_distance</t>
+          <t>fare_per_mile_per_trip_distance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1422,7 +1430,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>b74d39221ecb6e75</t>
+          <t>f3e14fa57fe854e7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1439,13 +1447,16 @@
         <v>3509466</v>
       </c>
       <c r="H12" t="n">
-        <v>0.867421375892653</v>
+        <v>0.04057522932726527</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8473806505494269</v>
+        <v>-0.7371659713029562</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.1590559465344401</v>
       </c>
       <c r="L12" t="n">
-        <v>0.86742</v>
+        <v>0.73717</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1454,31 +1465,42 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>very strong</t>
-        </is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>0.9694052765740944</v>
       </c>
       <c r="P12" t="n">
-        <v>0.7524198433555032</v>
+        <v>0.001646349234960168</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.231065593293843</v>
+        <v>3.854796059587181e-05</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.73995</v>
+        <v>0.74771</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>br_01bd146e</t>
-        </is>
-      </c>
-      <c r="V12" s="3" t="inlineStr"/>
-      <c r="W12" s="3" t="inlineStr"/>
+          <t>br_4e2a95f5</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>trip_distance_per_fare_per_mile</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>monotonic association is much stronger than the linear one; the relationship is probably nonlinear; 1 equivalent transformation(s) of the same columns gave the same effect within 0.01; reporting the simplest form; most subgroups show the opposite sign to the pooled correlation; the pooled value is an aggregation artifact</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1486,7 +1508,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>fare_amount</t>
+          <t>is_airport_pickup</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1496,12 +1518,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>585c40398a3fef87</t>
+          <t>917cbdee9f321842</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MECHANICAL (definitional)</t>
+          <t>empirical</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1510,19 +1532,19 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>3509466</v>
+        <v>2515206</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9656760855932028</v>
+        <v>0.6426310815998221</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9571350108978417</v>
+        <v>0.4426551110166427</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4230657610716627</v>
+        <v>0.1644203331945612</v>
       </c>
       <c r="L13" t="n">
-        <v>0.96568</v>
+        <v>0.64263</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1531,42 +1553,34 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>very strong</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>0.9994051036302739</v>
+        <v>0.9980040902668088</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9325303022866108</v>
+        <v>0.4129747070381572</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.163133031834264</v>
+        <v>51.00813560724194</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.71109</v>
+        <v>0.74564</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>br_866e1002</t>
-        </is>
-      </c>
-      <c r="V13" s="3" t="inlineStr">
-        <is>
-          <t>fare_amount; fare_amount; fare_amount</t>
-        </is>
-      </c>
-      <c r="W13" s="3" t="inlineStr">
-        <is>
-          <t>3 equivalent transformation(s) of the same columns gave the same effect within 0.01; reporting the simplest form</t>
-        </is>
-      </c>
+          <t>br_e2c1c529</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr"/>
+      <c r="W13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1574,7 +1588,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>log_trip_distance</t>
+          <t>average_speed_mph_times_trip_distance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1584,7 +1598,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>6de2708a5513d3c8</t>
+          <t>4371399e65b6f393</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1601,13 +1615,13 @@
         <v>3509466</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7001671976609333</v>
+        <v>0.7788165655343621</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8473806505494269</v>
+        <v>0.726311957694207</v>
       </c>
       <c r="L14" t="n">
-        <v>0.84738</v>
+        <v>0.77882</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1616,39 +1630,31 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>very strong</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0.4902341046803644</v>
+        <v>0.6065552427507392</v>
       </c>
       <c r="Q14" t="n">
-        <v>14.07130464097933</v>
+        <v>0.1315708166815401</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.69842</v>
+        <v>0.67374</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>br_01bd146e</t>
-        </is>
-      </c>
-      <c r="V14" s="3" t="inlineStr">
-        <is>
-          <t>log1p_trip_distance</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="inlineStr">
-        <is>
-          <t>1 equivalent transformation(s) of the same columns gave the same effect within 0.01; reporting the simplest form</t>
-        </is>
-      </c>
+          <t>br_4e2a95f5</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr"/>
+      <c r="W14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1656,7 +1662,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>is_airport_pickup</t>
+          <t>trip_distance_per_congestion_surcharge</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1666,55 +1672,69 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>grp:is_airport_pickup:total_amount</t>
+          <t>58da4195c6a392ec</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>empirical</t>
+          <t>MECHANICAL (definitional)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>grouped_eta_squared</t>
+          <t>pearson_spearman</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2515206</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.6426310816003343</v>
+        <v>2240818</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.9416425172184314</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.8785303492837994</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.2781229876218406</v>
       </c>
       <c r="L15" t="n">
-        <v>0.64263</v>
+        <v>0.94164</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>undetermined</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>strong</t>
-        </is>
+          <t>very strong</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>0.9984662896395945</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.8866906302334638</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>12.08690612387144</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6512</v>
+        <v>0.67039</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>br_56b66fb5</t>
+          <t>br_4e2a95f5</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr"/>
-      <c r="W15" s="3" t="inlineStr">
-        <is>
-          <t>is_airport_pickup is categorical; compared as group means, not as a correlation</t>
-        </is>
-      </c>
+      <c r="W15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1722,7 +1742,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>fare_per_mile</t>
+          <t>RatecodeID</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1732,7 +1752,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>118c265b17127fd2</t>
+          <t>grp:RatecodeID:total_amount</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1742,65 +1762,43 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>pearson_spearman</t>
+          <t>grouped_eta_squared</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>3509466</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.04054402311080481</v>
-      </c>
-      <c r="I16" t="n">
-        <v>-0.4522641312943602</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.0677329656948885</v>
+        <v>2515206</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.6788292533749694</v>
       </c>
       <c r="L16" t="n">
-        <v>0.45226</v>
+        <v>0.67883</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>undetermined</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>moderate</t>
-        </is>
-      </c>
-      <c r="O16" t="n">
-        <v>0.9748487559040943</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0.001643817810009474</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.003767970774903824</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
+          <t>strong</t>
+        </is>
       </c>
       <c r="S16" t="n">
-        <v>0.63797</v>
+        <v>0.6666299999999999</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>br_866e1002</t>
-        </is>
-      </c>
-      <c r="V16" s="3" t="inlineStr">
-        <is>
-          <t>fare_per_mile; fare_per_mile</t>
-        </is>
-      </c>
+          <t>br_a334d03d</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr"/>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>monotonic association is much stronger than the linear one; the relationship is probably nonlinear; 2 equivalent transformation(s) of the same columns gave the same effect within 0.01; reporting the simplest form</t>
+          <t>RatecodeID is categorical; compared as group means, not as a correlation</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1808,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>trip_distance_per_trip_duration_minutes</t>
+          <t>is_airport_pickup_minus_tip_fraction_of_fare</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1820,7 +1818,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>880f84238da823e3</t>
+          <t>8335ce51d7d81bd1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1834,16 +1832,19 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>3509466</v>
+        <v>2514623</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5473835801360865</v>
+        <v>0.5466552026825173</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3531235693623642</v>
+        <v>0.3473666814014659</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.1638635804954771</v>
       </c>
       <c r="L17" t="n">
-        <v>0.54738</v>
+        <v>0.54666</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1855,28 +1856,39 @@
           <t>strong</t>
         </is>
       </c>
+      <c r="O17" t="n">
+        <v>0.9509302593875516</v>
+      </c>
       <c r="P17" t="n">
-        <v>0.2996287838025994</v>
+        <v>0.2988319106198641</v>
       </c>
       <c r="Q17" t="n">
-        <v>104.1029636964781</v>
+        <v>34.59077513642316</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.57919</v>
+        <v>0.65498</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>br_01bd146e</t>
-        </is>
-      </c>
-      <c r="V17" s="3" t="inlineStr"/>
-      <c r="W17" s="3" t="inlineStr"/>
+          <t>br_4e2a95f5</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>tip_fraction_of_fare_minus_is_airport_pickup</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>1 equivalent transformation(s) of the same columns gave the same effect within 0.01; reporting the simplest form</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1884,7 +1896,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>trip_duration_minutes_per_trip_distance</t>
+          <t>is_airport_pickup</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1894,7 +1906,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>68230704e6c65c3b</t>
+          <t>grp:is_airport_pickup:total_amount</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1904,58 +1916,43 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>pearson_spearman</t>
+          <t>grouped_eta_squared</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>3509466</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.02612619849158769</v>
-      </c>
-      <c r="I18" t="n">
-        <v>-0.3531239375169539</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.04916244729839663</v>
+        <v>2515206</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.6426310816003343</v>
       </c>
       <c r="L18" t="n">
-        <v>0.35312</v>
+        <v>0.64263</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>undetermined</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>moderate</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>0.0006825782476218391</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.003691983085506913</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
+          <t>strong</t>
+        </is>
       </c>
       <c r="S18" t="n">
-        <v>0.47881</v>
+        <v>0.6512</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>br_01bd146e</t>
+          <t>br_e2c1c529</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr"/>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>monotonic association is much stronger than the linear one; the relationship is probably nonlinear</t>
+          <t>is_airport_pickup is categorical; compared as group means, not as a correlation</t>
         </is>
       </c>
     </row>
@@ -1965,7 +1962,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>fare_amount / trip_distance</t>
+          <t>congestion_surcharge_per_trip_distance</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1975,7 +1972,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2fc81ea1a5372f3d</t>
+          <t>c2f157d2609f44a7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1989,54 +1986,57 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>3509466</v>
+        <v>2515206</v>
       </c>
       <c r="H19" t="n">
-        <v>0.04054402311080481</v>
+        <v>-0.2136101002033965</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4522641312943602</v>
+        <v>-0.8163179431610647</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0677329656948885</v>
+        <v>0.2612396393095405</v>
       </c>
       <c r="L19" t="n">
-        <v>0.45226</v>
+        <v>0.81632</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>moderate</t>
-        </is>
+          <t>very strong</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0.977487832964769</v>
       </c>
       <c r="P19" t="n">
-        <v>0.001643817810009474</v>
+        <v>0.04562927490890509</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.003767970774903824</v>
+        <v>-1.12625056526446</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.42473</v>
+        <v>0.62709</v>
       </c>
       <c r="T19" t="n">
         <v>1</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>br_01bd146e</t>
+          <t>br_4e2a95f5</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr"/>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>monotonic association is much stronger than the linear one; the relationship is probably nonlinear; most subgroups show the opposite sign to the pooled correlation; the pooled value is an aggregation artifact</t>
+          <t>monotonic association is much stronger than the linear one; the relationship is probably nonlinear</t>
         </is>
       </c>
     </row>
@@ -2046,17 +2046,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>payment_type</t>
+          <t>average_speed_mph</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>fare_amount</t>
+          <t>total_amount</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>grp:payment_type:fare_amount</t>
+          <t>a114a3943dea72f3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2066,45 +2066,53 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>grouped_eta_squared</t>
+          <t>pearson_spearman</t>
         </is>
       </c>
       <c r="G20" t="n">
         <v>3509466</v>
       </c>
-      <c r="J20" t="n">
-        <v>0.1521138756208264</v>
+      <c r="H20" t="n">
+        <v>0.5473835801360867</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.3531237817140657</v>
       </c>
       <c r="L20" t="n">
-        <v>0.15211</v>
+        <v>0.54738</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>undetermined</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>weak</t>
-        </is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>0.2996287838025996</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.735049394941302</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.29091</v>
+        <v>0.60793</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>br_866e1002</t>
+          <t>br_6e01516d</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr"/>
-      <c r="W20" s="3" t="inlineStr">
-        <is>
-          <t>payment_type is categorical; compared as group means, not as a correlation</t>
-        </is>
-      </c>
+      <c r="W20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2112,7 +2120,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>passenger_count</t>
+          <t>average_speed_mph_per_passenger_count</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2122,7 +2130,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>7b89c356f3603a1e</t>
+          <t>30dc7e05c7def7da</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2136,19 +2144,16 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2515206</v>
+        <v>2501017</v>
       </c>
       <c r="H21" t="n">
-        <v>0.05567211900282587</v>
+        <v>0.524944561262767</v>
       </c>
       <c r="I21" t="n">
-        <v>0.03970968100948129</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.002354863652130918</v>
+        <v>0.2760167127792159</v>
       </c>
       <c r="L21" t="n">
-        <v>0.05567</v>
+        <v>0.52494</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -2157,42 +2162,31 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="O21" t="n">
-        <v>0.9775789746167172</v>
+          <t>strong</t>
+        </is>
       </c>
       <c r="P21" t="n">
-        <v>0.003099384834264805</v>
+        <v>0.2755667923993589</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.878440616791905</v>
+        <v>1.82891474088329</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.26818</v>
+        <v>0.6051800000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>br_e3d9ee52</t>
-        </is>
-      </c>
-      <c r="V21" s="3" t="inlineStr">
-        <is>
-          <t>log1p(passenger_count); log1p_passenger_count; abs_passenger_count</t>
-        </is>
-      </c>
-      <c r="W21" s="3" t="inlineStr">
-        <is>
-          <t>3 equivalent transformation(s) of the same columns gave the same effect within 0.01; reporting the simplest form</t>
-        </is>
-      </c>
+          <t>br_4e2a95f5</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr"/>
+      <c r="W21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2200,7 +2194,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>payment_type</t>
+          <t>average_speed_mph_times_passenger_count</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2210,7 +2204,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>grp:payment_type:total_amount</t>
+          <t>ffb69f70a0d9b159</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2220,45 +2214,53 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>grouped_eta_squared</t>
+          <t>pearson_spearman</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>3509466</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.08019928528122922</v>
+        <v>2515206</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.4850649121908158</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.2864942422513549</v>
       </c>
       <c r="L22" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.48506</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>undetermined</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>negligible</t>
-        </is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>0.2352879690386838</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.8644244599725373</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.25784</v>
+        <v>0.58495</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>br_866e1002</t>
+          <t>br_4e2a95f5</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr"/>
-      <c r="W22" s="3" t="inlineStr">
-        <is>
-          <t>payment_type is categorical; compared as group means, not as a correlation</t>
-        </is>
-      </c>
+      <c r="W22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2266,7 +2268,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>fare_amount / trip_duration_minutes</t>
+          <t>congestion_surcharge_times_trip_distance</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2276,7 +2278,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>352791f3bee86b93</t>
+          <t>eef57bf574ac0e5e</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2290,16 +2292,19 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>3509466</v>
+        <v>2515206</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1336236576299658</v>
+        <v>0.646587963663666</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.008121393679587731</v>
+        <v>0.5275201806403171</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.2624591147566981</v>
       </c>
       <c r="L23" t="n">
-        <v>0.13362</v>
+        <v>0.64659</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -2308,27 +2313,30 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>weak</t>
-        </is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0.9959990331693519</v>
       </c>
       <c r="P23" t="n">
-        <v>0.01785528187841032</v>
+        <v>0.4180759947547263</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.550057244100293</v>
+        <v>1.635740481719467</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.24343</v>
+        <v>0.57013</v>
       </c>
       <c r="T23" t="n">
         <v>1</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>br_e3d9ee52</t>
+          <t>br_4e2a95f5</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr"/>
@@ -2340,7 +2348,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>log1p_passenger_count</t>
+          <t>is_airport_pickup_plus_tip_fraction_of_fare</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2350,7 +2358,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>048288721cc6e798</t>
+          <t>737d2717a2de4d51</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2364,16 +2372,16 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2515206</v>
+        <v>2514623</v>
       </c>
       <c r="H24" t="n">
-        <v>0.06127356558580398</v>
+        <v>0.5142566256410299</v>
       </c>
       <c r="I24" t="n">
-        <v>0.03970968100948129</v>
+        <v>0.08316634892743088</v>
       </c>
       <c r="L24" t="n">
-        <v>0.06127</v>
+        <v>0.5142600000000001</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -2382,39 +2390,31 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0.003754449839597822</v>
+        <v>0.2644598770156984</v>
       </c>
       <c r="Q24" t="n">
-        <v>6.096257848517154</v>
+        <v>34.9945552533019</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.23036</v>
+        <v>0.5638</v>
       </c>
       <c r="T24" t="n">
         <v>1</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>br_01bd146e</t>
-        </is>
-      </c>
-      <c r="V24" s="3" t="inlineStr">
-        <is>
-          <t>abs_passenger_count</t>
-        </is>
-      </c>
-      <c r="W24" s="3" t="inlineStr">
-        <is>
-          <t>1 equivalent transformation(s) of the same columns gave the same effect within 0.01; reporting the simplest form</t>
-        </is>
-      </c>
+          <t>br_4e2a95f5</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr"/>
+      <c r="W24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>pickup_hour</t>
+          <t>fare_per_mile</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>grp:pickup_hour:total_amount</t>
+          <t>118c265b17127fd2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2442,43 +2442,62 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>grouped_eta_squared</t>
+          <t>pearson_spearman</t>
         </is>
       </c>
       <c r="G25" t="n">
         <v>3509466</v>
       </c>
-      <c r="J25" t="n">
-        <v>0.05892233745550347</v>
+      <c r="H25" t="n">
+        <v>0.04054402311080481</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.4522641312943602</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.0677329656948885</v>
       </c>
       <c r="L25" t="n">
-        <v>0.05892</v>
+        <v>0.45226</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>undetermined</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>negligible</t>
-        </is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>0.001643817810009474</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.003767970774903824</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.22271</v>
+        <v>0.55993</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>br_56b66fb5</t>
-        </is>
-      </c>
-      <c r="V25" s="3" t="inlineStr"/>
+          <t>br_97f99819</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>log1p_fare_per_mile; abs_fare_per_mile; log(fare_per_mile)</t>
+        </is>
+      </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>pickup_hour is categorical; compared as group means, not as a correlation</t>
+          <t>monotonic association is much stronger than the linear one; the relationship is probably nonlinear; 3 equivalent transformation(s) of the same columns gave the same effect within 0.01; reporting the simplest form; most subgroups show the opposite sign to the pooled correlation; the pooled value is an aggregation artifact</t>
         </is>
       </c>
     </row>
@@ -2488,17 +2507,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>pickup_hour</t>
+          <t>log1p_average_speed_mph</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>fare_amount</t>
+          <t>total_amount</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>grp:pickup_hour:fare_amount</t>
+          <t>03f7cba18dd845bd</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2508,45 +2527,53 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>grouped_eta_squared</t>
+          <t>pearson_spearman</t>
         </is>
       </c>
       <c r="G26" t="n">
         <v>3509466</v>
       </c>
-      <c r="J26" t="n">
-        <v>0.07761467446433983</v>
+      <c r="H26" t="n">
+        <v>0.4349123951130241</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.3531240505434882</v>
       </c>
       <c r="L26" t="n">
-        <v>0.07761</v>
+        <v>0.43491</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>undetermined</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>negligible</t>
-        </is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>0.1891487914229472</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>17.91355648281625</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.21164</v>
+        <v>0.52433</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>br_72f96e3a</t>
+          <t>br_4e2a95f5</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr"/>
-      <c r="W26" s="3" t="inlineStr">
-        <is>
-          <t>pickup_hour is categorical; compared as group means, not as a correlation</t>
-        </is>
-      </c>
+      <c r="W26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2554,7 +2581,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>pickup_day_of_week</t>
+          <t>tip_fraction_of_fare_times_trip_duration_minutes</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2564,7 +2591,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>grp:pickup_day_of_week:total_amount</t>
+          <t>04f2d88dad5f061a</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2574,45 +2601,53 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>grouped_eta_squared</t>
+          <t>pearson_spearman</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>3509466</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.05148141791777337</v>
+        <v>3508357</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.4277061467199243</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.1812392020107477</v>
       </c>
       <c r="L27" t="n">
-        <v>0.05148</v>
+        <v>0.42771</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>undetermined</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>negligible</t>
-        </is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>0.1829325479420054</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.929713907839949</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0.20864</v>
+        <v>0.52053</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>br_9471cd97</t>
+          <t>br_4e2a95f5</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr"/>
-      <c r="W27" s="3" t="inlineStr">
-        <is>
-          <t>pickup_day_of_week is categorical; compared as group means, not as a correlation</t>
-        </is>
-      </c>
+      <c r="W27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2620,17 +2655,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>VendorID</t>
+          <t>RatecodeID</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>fare_amount</t>
+          <t>total_amount</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>grp:VendorID:fare_amount</t>
+          <t>f4f02ee5436277f3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2640,43 +2675,58 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>grouped_eta_squared</t>
+          <t>pearson_spearman</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>3509466</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.04336664643217196</v>
+        <v>2515206</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.0912542477078475</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.3760355473923238</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.1454265720998692</v>
       </c>
       <c r="L28" t="n">
-        <v>0.04337</v>
+        <v>0.37604</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>undetermined</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>negligible</t>
-        </is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>0.00832733772472519</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.1025951961473406</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.15834</v>
+        <v>0.51688</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>br_9471cd97</t>
+          <t>br_a334d03d</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr"/>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>VendorID is categorical; compared as group means, not as a correlation</t>
+          <t>monotonic association is much stronger than the linear one; the relationship is probably nonlinear</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2736,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VendorID</t>
+          <t>congestion_surcharge_times_fare_per_mile</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2696,53 +2746,71 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>grp:VendorID:total_amount</t>
+          <t>3a61581b9fb15b27</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>empirical</t>
+          <t>MECHANICAL (definitional)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>grouped_eta_squared</t>
+          <t>pearson_spearman</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>3509466</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.02868398323979627</v>
+        <v>2515206</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-0.02741945570533132</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-0.554163593424801</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.1022315333061821</v>
       </c>
       <c r="L29" t="n">
-        <v>0.02868</v>
+        <v>0.55416</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>undetermined</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>negligible</t>
-        </is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>0.8247963285429323</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.0007518265511766265</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>-0.006357048543617688</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.15573</v>
+        <v>0.50669</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>br_72f96e3a</t>
+          <t>br_4e2a95f5</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>VendorID is categorical; compared as group means, not as a correlation</t>
+          <t>monotonic association is much stronger than the linear one; the relationship is probably nonlinear</t>
         </is>
       </c>
     </row>
@@ -2752,17 +2820,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>is_airport_pickup</t>
+          <t>tip_fraction_of_fare_per_trip_duration_minutes</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>total_per_mile</t>
+          <t>total_amount</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>grp:is_airport_pickup:total_per_mile</t>
+          <t>9eb4345d8ef95ec7</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2772,43 +2840,58 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>grouped_eta_squared</t>
+          <t>pearson_spearman</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2515206</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.03857070853987054</v>
+        <v>3508357</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-0.11559946947529</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-0.3876741558047004</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.1443706583101716</v>
       </c>
       <c r="L30" t="n">
-        <v>0.03857</v>
+        <v>0.38767</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>undetermined</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>negligible</t>
-        </is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>0.0133632373429685</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>-30.38874017677642</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.14902</v>
+        <v>0.49873</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>br_9471cd97</t>
+          <t>br_4e2a95f5</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>is_airport_pickup is categorical; compared as group means, not as a correlation</t>
+          <t>monotonic association is much stronger than the linear one; the relationship is probably nonlinear</t>
         </is>
       </c>
     </row>
@@ -2818,17 +2901,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>is_rush_hour</t>
+          <t>log_average_speed_mph</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>fare_amount</t>
+          <t>total_amount</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>grp:is_rush_hour:fare_amount</t>
+          <t>8e06bea837bc3362</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2838,41 +2921,994 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>grouped_eta_squared</t>
+          <t>pearson_spearman</t>
         </is>
       </c>
       <c r="G31" t="n">
         <v>3509466</v>
       </c>
-      <c r="J31" t="n">
-        <v>0.003241516268364303</v>
+      <c r="H31" t="n">
+        <v>0.3466719325017407</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.3531239113044003</v>
       </c>
       <c r="L31" t="n">
-        <v>0.00324</v>
+        <v>0.35312</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>0.1201814287844914</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>10.75272286190757</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.47881</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>br_4e2a95f5</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr"/>
+      <c r="W31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>fare_per_mile_per_congestion_surcharge</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>total_amount</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>202d02f5d404ff15</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>MECHANICAL (definitional)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>pearson_spearman</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>2240818</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-0.006310558879373152</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-0.5307054384978036</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.09666797239099795</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.53071</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>3.982315337003533e-05</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>-0.007226388336885422</v>
+      </c>
+      <c r="R32" t="n">
+        <v>3.500392944442411e-21</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.45576</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>br_4e2a95f5</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr"/>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>monotonic association is much stronger than the linear one; the relationship is probably nonlinear</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>passenger_count_per_average_speed_mph</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>total_amount</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1bd6232701cd1677</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>empirical</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>pearson_spearman</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>2515206</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-0.06710396617964622</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-0.2634808504466137</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.26348</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>0.004502942277039103</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>-3.947230368638753</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.4485</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>br_4e2a95f5</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr"/>
+      <c r="W33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>payment_type</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>total_amount</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>f8aa7d74cd50118b</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>empirical</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>pearson_spearman</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>3509466</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-0.06933681668964253</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-0.2309094199465334</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.23091</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>0.004807594148653092</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>-2.24228225584734</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.4173</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>br_6e01516d</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr"/>
+      <c r="W34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>tip_fraction_of_fare</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>total_amount</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>300a6e5e837e30b1</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>empirical</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>pearson_spearman</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>3508357</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-0.07602972303767626</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-0.2303174771234442</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.23032</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>0.00578051878518576</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>-8.311849249613013</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.41683</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>br_97f99819</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>tip_fraction_of_fare; log1p_tip_fraction_of_fare; abs_tip_fraction_of_fare</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>3 equivalent transformation(s) of the same columns gave the same effect within 0.01; reporting the simplest form</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>congestion_surcharge</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>total_amount</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>17d4582668b96832</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>MECHANICAL (definitional)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>pearson_spearman</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>2515206</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-0.3087619890141536</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-0.2678235853551849</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>0.09533396585997633</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>-8.909193978732603</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.37678</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>br_a334d03d</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>abs_congestion_surcharge; log1p_congestion_surcharge</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>2 equivalent transformation(s) of the same columns gave the same effect within 0.01; reporting the simplest form</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>congestion_surcharge_per_fare_per_mile</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>total_amount</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>5e2874562840a0dc</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>MECHANICAL (definitional)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>pearson_spearman</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>2514623</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.02699458177962337</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.2623655682680891</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.26237</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>0.0007287074454567742</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.6018378735207764</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.33279</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>br_4e2a95f5</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr"/>
+      <c r="W37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>payment_type</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>total_amount</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>grp:payment_type:total_amount</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>empirical</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>grouped_eta_squared</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>3509466</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.08019928528122922</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.08019999999999999</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
           <t>undetermined</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>negligible</t>
         </is>
       </c>
-      <c r="S31" t="n">
-        <v>0.06807000000000001</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>br_56b66fb5</t>
-        </is>
-      </c>
-      <c r="V31" s="3" t="inlineStr"/>
-      <c r="W31" s="3" t="inlineStr">
+      <c r="S38" t="n">
+        <v>0.25784</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>br_8d8e2f72</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr"/>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>payment_type is categorical; compared as group means, not as a correlation</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>passenger_count</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>total_amount</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>7b89c356f3603a1e</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>empirical</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>pearson_spearman</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>2515206</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.05567211900282587</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.03970968100948129</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.05567</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>0.003099384834264805</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.878440616791905</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.2322</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>br_97f99819</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t>log1p_passenger_count; abs_passenger_count</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t>2 equivalent transformation(s) of the same columns gave the same effect within 0.01; reporting the simplest form</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>pickup_hour</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>total_amount</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>grp:pickup_hour:total_amount</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>empirical</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>grouped_eta_squared</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>3509466</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.05892233745550347</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.05892</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>undetermined</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
+      </c>
+      <c r="S40" t="n">
+        <v>0.22271</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>br_e2c1c529</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr"/>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t>pickup_hour is categorical; compared as group means, not as a correlation</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>pickup_day_of_week</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>total_amount</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>grp:pickup_day_of_week:total_amount</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>empirical</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>grouped_eta_squared</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>3509466</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.05148141791777337</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.05148</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>undetermined</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
+      </c>
+      <c r="S41" t="n">
+        <v>0.20864</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>br_e2c1c529</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr"/>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t>pickup_day_of_week is categorical; compared as group means, not as a correlation</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>VendorID</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>total_amount</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>grp:VendorID:total_amount</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>empirical</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>grouped_eta_squared</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>3509466</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.02868398323979627</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.02868</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>undetermined</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
+      </c>
+      <c r="S42" t="n">
+        <v>0.15573</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>br_6e01516d</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr"/>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t>VendorID is categorical; compared as group means, not as a correlation</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>is_airport_pickup</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>total_per_mile</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>grp:is_airport_pickup:total_per_mile</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>empirical</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>grouped_eta_squared</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>2515206</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.03857070853987054</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.03857</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>undetermined</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
+      </c>
+      <c r="S43" t="n">
+        <v>0.14902</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>br_a334d03d</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr"/>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t>is_airport_pickup is categorical; compared as group means, not as a correlation</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>is_rush_hour</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>total_amount</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>grp:is_rush_hour:total_amount</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>empirical</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>grouped_eta_squared</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>3509466</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.01259207470513526</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.01259</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>undetermined</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
+      </c>
+      <c r="S44" t="n">
+        <v>0.09941</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>br_8d8e2f72</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr"/>
+      <c r="W44" s="3" t="inlineStr">
         <is>
           <t>is_rush_hour is categorical; compared as group means, not as a correlation</t>
         </is>
